--- a/Employees/Employee_View.xlsx
+++ b/Employees/Employee_View.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.My computer\Vulyk Clinic Website\Employees\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711100E9-6CC8-4657-A02F-D646E79DDA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3E8029-D62B-4A9C-988F-6AB89980163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="386">
   <si>
     <t>Employee View</t>
   </si>
@@ -1150,9 +1150,6 @@
     <t>Дорослий та дитячий хірург</t>
   </si>
   <si>
-    <t>Медсестра (в декруті)</t>
-  </si>
-  <si>
     <t>Менеджер з адміністративної діяльності</t>
   </si>
   <si>
@@ -1171,10 +1168,16 @@
     <t>Тавридзька</t>
   </si>
   <si>
-    <t>Дитячий психотерапевт</t>
-  </si>
-  <si>
     <t>Медична Директор, Сімейна лікарка</t>
+  </si>
+  <si>
+    <t>Дитячий психіатр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медсестра </t>
+  </si>
+  <si>
+    <t>Тичини (декрет)</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1571,7 @@
   <cols>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
@@ -2313,10 +2316,10 @@
         <v>50</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>52</v>
@@ -2396,7 +2399,7 @@
         <v>62</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>367</v>
@@ -2668,7 +2671,7 @@
         <v>144</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I18" t="s">
         <v>372</v>
@@ -3505,7 +3508,7 @@
         <v>62</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>368</v>
@@ -3771,7 +3774,7 @@
         <v>110</v>
       </c>
       <c r="I34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>52</v>
@@ -4461,7 +4464,7 @@
         <v>62</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>367</v>
@@ -4540,13 +4543,13 @@
         <v>96</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>81</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>368</v>
@@ -4557,7 +4560,7 @@
         <v>123</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>81</v>

--- a/Employees/Employee_View.xlsx
+++ b/Employees/Employee_View.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.My computer\Vulyk Clinic Website\Employees\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3E8029-D62B-4A9C-988F-6AB89980163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0382D7-C30C-4B98-BA67-9632E5F54476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="389">
   <si>
     <t>Employee View</t>
   </si>
@@ -1178,6 +1178,15 @@
   </si>
   <si>
     <t>Тичини (декрет)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ірина </t>
+  </si>
+  <si>
+    <t>Ярема</t>
+  </si>
+  <si>
+    <t>Демчук</t>
   </si>
 </sst>
 </file>
@@ -1566,12 +1575,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ49"/>
+  <dimension ref="A1:AQ51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
@@ -1915,6 +1925,9 @@
       <c r="I5" t="s">
         <v>369</v>
       </c>
+      <c r="J5" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -2204,6 +2217,9 @@
       <c r="I10" t="s">
         <v>368</v>
       </c>
+      <c r="J10" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
@@ -2292,6 +2308,9 @@
       <c r="I12" t="s">
         <v>369</v>
       </c>
+      <c r="J12" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -3058,6 +3077,9 @@
       <c r="I23" t="s">
         <v>368</v>
       </c>
+      <c r="J23" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -3484,6 +3506,9 @@
       <c r="I29" t="s">
         <v>367</v>
       </c>
+      <c r="J29" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
@@ -3747,6 +3772,9 @@
       <c r="I33" t="s">
         <v>367</v>
       </c>
+      <c r="J33" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
@@ -3965,6 +3993,9 @@
       <c r="I37" t="s">
         <v>368</v>
       </c>
+      <c r="J37" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
@@ -4198,6 +4229,9 @@
       <c r="I41" t="s">
         <v>372</v>
       </c>
+      <c r="J41" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
@@ -4289,6 +4323,9 @@
       <c r="I43" t="s">
         <v>368</v>
       </c>
+      <c r="J43" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -4537,6 +4574,9 @@
       <c r="I47" t="s">
         <v>372</v>
       </c>
+      <c r="J47" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.3">
       <c r="C48" s="3" t="s">
@@ -4554,8 +4594,11 @@
       <c r="I48" s="3" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="49" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J48" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C49" s="3" t="s">
         <v>123</v>
       </c>
@@ -4570,6 +4613,61 @@
       </c>
       <c r="I49" s="3" t="s">
         <v>368</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C50" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>388</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
